--- a/artfynd/A 41421-2025 artfynd.xlsx
+++ b/artfynd/A 41421-2025 artfynd.xlsx
@@ -675,60 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86866104</v>
+        <v>91164518</v>
       </c>
       <c r="B2" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101246</v>
+        <v>2023</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -736,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540027.5488857756</v>
+        <v>540144</v>
       </c>
       <c r="R2" t="n">
-        <v>6231746.391001889</v>
+        <v>6231876</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -766,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,57 +761,85 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Schmidt</t>
+          <t>Niclas Wahlgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Schmidt</t>
+          <t>Niclas Wahlgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91164518</v>
+        <v>86866104</v>
       </c>
       <c r="B3" t="n">
-        <v>89783</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2023</v>
+        <v>101246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540143.8497211625</v>
+        <v>540028</v>
       </c>
       <c r="R3" t="n">
-        <v>6231876.430644412</v>
+        <v>6231746</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -882,22 +877,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,30 +895,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niclas Wahlgren</t>
+          <t>Andreas Schmidt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niclas Wahlgren</t>
+          <t>Andreas Schmidt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 41421-2025 artfynd.xlsx
+++ b/artfynd/A 41421-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91164518</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86866104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134038867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,8 +1154,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134249388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41421-2025 artfynd.xlsx
+++ b/artfynd/A 41421-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,132 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134249388</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136153992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9417</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tullaretorpet, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>540109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6231765</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Augerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Död hane</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136153992</t>
         </is>
       </c>
     </row>
@@ -1166,6 +1292,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
